--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T13:03:58+00:00</t>
+    <t>2025-05-14T14:13:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T08:04:56+00:00</t>
+    <t>2025-05-21T13:48:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T13:48:36+00:00</t>
+    <t>2025-05-23T10:50:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/StructureDefinition-Validateur.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-23T10:50:09+00:00</t>
+    <t>2025-05-23T12:29:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
